--- a/src/grafs_e/data/scenario_region/Linear/Alsace.xlsx
+++ b/src/grafs_e/data/scenario_region/Linear/Alsace.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\faustega\Documents\These\isterre-dynamic-modeling\grafs-e-project\grafs-e\src\grafs_e\data\scenario_region\Linear\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\faustega\Documents\These\scenario\Linear\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{605BF092-7B9B-444D-B04C-877CB5A04941}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4BBB534-F8BF-4C2A-BD59-D45C1D052492}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-3312" yWindow="-17388" windowWidth="30936" windowHeight="16896" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="161">
   <si>
     <t>excel sheet for scenario writing</t>
   </si>
@@ -322,6 +322,9 @@
     <t>Weight energy</t>
   </si>
   <si>
+    <t>Weight methaniser input</t>
+  </si>
+  <si>
     <t>N recycling rate of human excretion in urban area</t>
   </si>
   <si>
@@ -485,6 +488,24 @@
   </si>
   <si>
     <t>Poultry dairy productivity</t>
+  </si>
+  <si>
+    <t>Share of crop residues in methaniser</t>
+  </si>
+  <si>
+    <t>Adapted from ONRB data</t>
+  </si>
+  <si>
+    <t>Share of green waste in methaniser</t>
+  </si>
+  <si>
+    <t>Share of dedicated culture in methaniser</t>
+  </si>
+  <si>
+    <t>Share of animal food industry in methaniser</t>
+  </si>
+  <si>
+    <t>Share of livestock effluent in methaniser</t>
   </si>
 </sst>
 </file>
@@ -1848,7 +1869,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:E57"/>
+  <dimension ref="A1:E62"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
@@ -1925,10 +1946,10 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C7">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="E7" t="s">
         <v>94</v>
@@ -1936,7 +1957,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B8" t="s">
         <v>24</v>
@@ -1947,7 +1968,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B9" t="s">
         <v>24</v>
@@ -1958,7 +1979,7 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B10" t="s">
         <v>24</v>
@@ -1969,7 +1990,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B11" t="s">
         <v>24</v>
@@ -1980,10 +2001,10 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E12" t="s">
         <v>33</v>
@@ -1991,10 +2012,10 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
+        <v>106</v>
+      </c>
+      <c r="B13" t="s">
         <v>105</v>
-      </c>
-      <c r="B13" t="s">
-        <v>104</v>
       </c>
       <c r="E13" t="s">
         <v>33</v>
@@ -2002,10 +2023,10 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B14" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E14" t="s">
         <v>33</v>
@@ -2013,10 +2034,10 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B15" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E15" t="s">
         <v>33</v>
@@ -2024,10 +2045,10 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B16" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E16" t="s">
         <v>33</v>
@@ -2035,10 +2056,10 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B17" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E17" t="s">
         <v>33</v>
@@ -2046,7 +2067,7 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B18" t="s">
         <v>24</v>
@@ -2057,7 +2078,7 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B19" t="s">
         <v>24</v>
@@ -2068,7 +2089,7 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B20" t="s">
         <v>24</v>
@@ -2079,7 +2100,7 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B21" t="s">
         <v>24</v>
@@ -2090,7 +2111,7 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B22" t="s">
         <v>24</v>
@@ -2101,7 +2122,7 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B23" t="s">
         <v>24</v>
@@ -2112,7 +2133,7 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B24" t="s">
         <v>24</v>
@@ -2123,7 +2144,7 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B25" t="s">
         <v>24</v>
@@ -2134,7 +2155,7 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B26" t="s">
         <v>24</v>
@@ -2145,7 +2166,7 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B27" t="s">
         <v>24</v>
@@ -2156,7 +2177,7 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B28" t="s">
         <v>24</v>
@@ -2167,7 +2188,7 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B29" t="s">
         <v>24</v>
@@ -2178,7 +2199,7 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B30" t="s">
         <v>24</v>
@@ -2189,7 +2210,7 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B31" t="s">
         <v>24</v>
@@ -2200,7 +2221,7 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B32" t="s">
         <v>24</v>
@@ -2211,7 +2232,7 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B33" t="s">
         <v>24</v>
@@ -2222,7 +2243,7 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B34" t="s">
         <v>24</v>
@@ -2233,7 +2254,7 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B35" t="s">
         <v>24</v>
@@ -2244,7 +2265,7 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B36" t="s">
         <v>24</v>
@@ -2255,7 +2276,7 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B37" t="s">
         <v>24</v>
@@ -2266,7 +2287,7 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B38" t="s">
         <v>24</v>
@@ -2277,7 +2298,7 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B39" t="s">
         <v>24</v>
@@ -2288,7 +2309,7 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B40" t="s">
         <v>24</v>
@@ -2299,7 +2320,7 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B41" t="s">
         <v>24</v>
@@ -2310,10 +2331,10 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B42" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E42" t="s">
         <v>28</v>
@@ -2321,10 +2342,10 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
+        <v>137</v>
+      </c>
+      <c r="B43" t="s">
         <v>136</v>
-      </c>
-      <c r="B43" t="s">
-        <v>135</v>
       </c>
       <c r="E43" t="s">
         <v>28</v>
@@ -2332,10 +2353,10 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B44" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E44" t="s">
         <v>28</v>
@@ -2343,10 +2364,10 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B45" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E45" t="s">
         <v>28</v>
@@ -2354,10 +2375,10 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B46" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E46" t="s">
         <v>28</v>
@@ -2365,10 +2386,10 @@
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B47" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E47" t="s">
         <v>28</v>
@@ -2376,112 +2397,182 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B48" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E48" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
+        <v>145</v>
+      </c>
+      <c r="B49" t="s">
+        <v>143</v>
+      </c>
+      <c r="E49" t="s">
         <v>144</v>
-      </c>
-      <c r="B49" t="s">
-        <v>142</v>
-      </c>
-      <c r="E49" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B50" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E50" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B51" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E51" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B52" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E52" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B53" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E53" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B54" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E54" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
+        <v>152</v>
+      </c>
+      <c r="B55" t="s">
         <v>151</v>
       </c>
-      <c r="B55" t="s">
-        <v>150</v>
-      </c>
       <c r="E55" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B56" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E56" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B57" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E57" t="s">
-        <v>143</v>
+        <v>144</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
+        <v>155</v>
+      </c>
+      <c r="B58" t="s">
+        <v>136</v>
+      </c>
+      <c r="C58">
+        <v>0.06</v>
+      </c>
+      <c r="E58" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A59" t="s">
+        <v>157</v>
+      </c>
+      <c r="B59" t="s">
+        <v>136</v>
+      </c>
+      <c r="C59">
+        <v>0.02</v>
+      </c>
+      <c r="E59" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A60" t="s">
+        <v>158</v>
+      </c>
+      <c r="B60" t="s">
+        <v>136</v>
+      </c>
+      <c r="C60">
+        <v>0.09</v>
+      </c>
+      <c r="E60" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
+        <v>159</v>
+      </c>
+      <c r="B61" t="s">
+        <v>136</v>
+      </c>
+      <c r="C61">
+        <v>0.04</v>
+      </c>
+      <c r="E61" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
+        <v>160</v>
+      </c>
+      <c r="B62" t="s">
+        <v>136</v>
+      </c>
+      <c r="C62">
+        <v>0.79</v>
+      </c>
+      <c r="E62" t="s">
+        <v>156</v>
       </c>
     </row>
   </sheetData>

--- a/src/grafs_e/data/scenario_region/Linear/Alsace.xlsx
+++ b/src/grafs_e/data/scenario_region/Linear/Alsace.xlsx
@@ -801,38 +801,43 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Crops</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Area proportion (%)</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Enforce Area</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>b</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>r2</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Straw to Grain Ratio</t>
         </is>
       </c>
     </row>
@@ -857,6 +862,9 @@
       <c r="F2" t="n">
         <v>0.57</v>
       </c>
+      <c r="G2" t="n">
+        <v>0.021</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -879,6 +887,9 @@
       <c r="F3" t="n">
         <v>0.61</v>
       </c>
+      <c r="G3" t="n">
+        <v>0.023</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -901,6 +912,9 @@
       <c r="F4" t="n">
         <v>0.53</v>
       </c>
+      <c r="G4" t="n">
+        <v>0.021</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -923,11 +937,14 @@
       <c r="F5" t="n">
         <v>0.16</v>
       </c>
+      <c r="G5" t="n">
+        <v>0.017</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Grain maize</t>
+          <t>Maize</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -945,6 +962,9 @@
       <c r="F6" t="n">
         <v>0.88</v>
       </c>
+      <c r="G6" t="n">
+        <v>0.022</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -967,6 +987,9 @@
       <c r="F7" t="n">
         <v>0</v>
       </c>
+      <c r="G7" t="n">
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -989,231 +1012,264 @@
       <c r="F8" t="n">
         <v>0.5600000000000001</v>
       </c>
+      <c r="G8" t="n">
+        <v>0.022</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Straw</t>
+          <t>Rapeseed</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>1.31239542665923</v>
       </c>
       <c r="C9" t="b">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0.95</v>
+        <v>0.8</v>
       </c>
       <c r="E9" t="n">
-        <v>115.85</v>
+        <v>129.25</v>
       </c>
       <c r="F9" t="n">
-        <v>0.34</v>
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="G9" t="n">
+        <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Rapeseed</t>
+          <t>Sunflower</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.31239542665923</v>
+        <v>0.2971625766871165</v>
       </c>
       <c r="C10" t="b">
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8</v>
+        <v>0.46</v>
       </c>
       <c r="E10" t="n">
-        <v>129.25</v>
+        <v>63.7</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.88</v>
+      </c>
+      <c r="G10" t="n">
+        <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sunflower</t>
+          <t>Soybean</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2971625766871165</v>
+        <v>0.7869143892916899</v>
       </c>
       <c r="C11" t="b">
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>0.46</v>
+        <v>0.65</v>
       </c>
       <c r="E11" t="n">
-        <v>63.7</v>
+        <v>184.16</v>
       </c>
       <c r="F11" t="n">
-        <v>0.88</v>
+        <v>0.96</v>
+      </c>
+      <c r="G11" t="n">
+        <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Soybean</t>
+          <t>Other oil crops</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.7869143892916899</v>
+        <v>0.02091466815393196</v>
       </c>
       <c r="C12" t="b">
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>0.65</v>
+        <v>0.75</v>
       </c>
       <c r="E12" t="n">
-        <v>184.16</v>
+        <v>46.57</v>
       </c>
       <c r="F12" t="n">
-        <v>0.96</v>
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Other oil crops</t>
+          <t>Horse beans and faba beans</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.02091466815393196</v>
+        <v>0.04749372559955382</v>
       </c>
       <c r="C13" t="b">
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>0.75</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>46.57</v>
+        <v>110.21</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>0.73</v>
+      </c>
+      <c r="G13" t="n">
+        <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Horse beans and faba beans</t>
+          <t>Peas</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.04749372559955382</v>
+        <v>0.03485778025655326</v>
       </c>
       <c r="C14" t="b">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="E14" t="n">
-        <v>110.21</v>
+        <v>158.81</v>
       </c>
       <c r="F14" t="n">
-        <v>0.73</v>
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="G14" t="n">
+        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Peas</t>
+          <t>Other protein crops</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.03485778025655326</v>
+        <v>0</v>
       </c>
       <c r="C15" t="b">
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="E15" t="n">
-        <v>158.81</v>
+        <v>85.27</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.76</v>
+      </c>
+      <c r="G15" t="n">
+        <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Other protein crops</t>
+          <t>Sugar beet</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>2.88622420524261</v>
       </c>
       <c r="C16" t="b">
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7</v>
+        <v>0.77</v>
       </c>
       <c r="E16" t="n">
-        <v>85.27</v>
+        <v>190.75</v>
       </c>
       <c r="F16" t="n">
-        <v>0.76</v>
+        <v>0.78</v>
+      </c>
+      <c r="G16" t="n">
+        <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sugar beet</t>
+          <t>Potatoes</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.88622420524261</v>
+        <v>0.511973647518126</v>
       </c>
       <c r="C17" t="b">
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.77</v>
+        <v>0.53</v>
       </c>
       <c r="E17" t="n">
-        <v>190.75</v>
+        <v>82.66</v>
       </c>
       <c r="F17" t="n">
-        <v>0.78</v>
+        <v>0.29</v>
+      </c>
+      <c r="G17" t="n">
+        <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Potatoes</t>
+          <t>Other roots</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.511973647518126</v>
+        <v>0</v>
       </c>
       <c r="C18" t="b">
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>0.53</v>
+        <v>0.79</v>
       </c>
       <c r="E18" t="n">
-        <v>82.66</v>
+        <v>179.89</v>
       </c>
       <c r="F18" t="n">
-        <v>0.29</v>
+        <v>0.66</v>
+      </c>
+      <c r="G18" t="n">
+        <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Other roots</t>
+          <t>Green peas</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1223,19 +1279,22 @@
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>0.79</v>
+        <v>0.41</v>
       </c>
       <c r="E19" t="n">
-        <v>179.89</v>
+        <v>22.21</v>
       </c>
       <c r="F19" t="n">
-        <v>0.66</v>
+        <v>0.3</v>
+      </c>
+      <c r="G19" t="n">
+        <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Green peas</t>
+          <t>Dry beans</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -1245,19 +1304,22 @@
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>0.41</v>
+        <v>0.55</v>
       </c>
       <c r="E20" t="n">
-        <v>22.21</v>
+        <v>96</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3</v>
+        <v>0.96</v>
+      </c>
+      <c r="G20" t="n">
+        <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Dry beans</t>
+          <t>Green beans</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1270,16 +1332,19 @@
         <v>0.55</v>
       </c>
       <c r="E21" t="n">
-        <v>96</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="F21" t="n">
-        <v>0.96</v>
+        <v>0.76</v>
+      </c>
+      <c r="G21" t="n">
+        <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Green beans</t>
+          <t>Dry vegetables</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -1289,19 +1354,22 @@
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>0.55</v>
+        <v>0.99</v>
       </c>
       <c r="E22" t="n">
-        <v>90.59999999999999</v>
+        <v>199.38</v>
       </c>
       <c r="F22" t="n">
-        <v>0.76</v>
+        <v>1</v>
+      </c>
+      <c r="G22" t="n">
+        <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Dry vegetables</t>
+          <t>Dry fruits</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1311,19 +1379,22 @@
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>0.99</v>
+        <v>0.59</v>
       </c>
       <c r="E23" t="n">
-        <v>199.38</v>
+        <v>38.04</v>
       </c>
       <c r="F23" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Dry fruits</t>
+          <t>Squash and melons</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -1333,19 +1404,22 @@
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>0.59</v>
+        <v>0.73</v>
       </c>
       <c r="E24" t="n">
-        <v>38.04</v>
+        <v>315.54</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>0.73</v>
+      </c>
+      <c r="G24" t="n">
+        <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Squash and melons</t>
+          <t>Cabbage</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1355,19 +1429,22 @@
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="E25" t="n">
-        <v>315.54</v>
+        <v>264.41</v>
       </c>
       <c r="F25" t="n">
-        <v>0.73</v>
+        <v>0.55</v>
+      </c>
+      <c r="G25" t="n">
+        <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Cabbage</t>
+          <t>Leaves vegetables</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1377,19 +1454,22 @@
         <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>0.7</v>
+        <v>0.85</v>
       </c>
       <c r="E26" t="n">
-        <v>264.41</v>
+        <v>29.99</v>
       </c>
       <c r="F26" t="n">
-        <v>0.55</v>
+        <v>0.19</v>
+      </c>
+      <c r="G26" t="n">
+        <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Leaves vegetables</t>
+          <t>Fruits</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1399,19 +1479,22 @@
         <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>0.85</v>
+        <v>0.53</v>
       </c>
       <c r="E27" t="n">
-        <v>29.99</v>
+        <v>21.39</v>
       </c>
       <c r="F27" t="n">
-        <v>0.19</v>
+        <v>0.52</v>
+      </c>
+      <c r="G27" t="n">
+        <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Fruits</t>
+          <t>Olives</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -1421,19 +1504,22 @@
         <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>0.53</v>
+        <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>21.39</v>
+        <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>0.52</v>
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Olives</t>
+          <t>Citrus</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1450,12 +1536,15 @@
       </c>
       <c r="F29" t="n">
         <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Citrus</t>
+          <t>Hemp</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -1465,19 +1554,22 @@
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>0.46</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>17.18</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>0.12</v>
+      </c>
+      <c r="G30" t="n">
+        <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Hemp</t>
+          <t>Flax</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1487,142 +1579,138 @@
         <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>0.46</v>
+        <v>0.61</v>
       </c>
       <c r="E31" t="n">
-        <v>17.18</v>
+        <v>12.19</v>
       </c>
       <c r="F31" t="n">
-        <v>0.12</v>
+        <v>0.95</v>
+      </c>
+      <c r="G31" t="n">
+        <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Flax</t>
+          <t>Forage maize</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0</v>
+        <v>5.361562325711099</v>
       </c>
       <c r="C32" t="b">
         <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>0.61</v>
+        <v>0.84</v>
       </c>
       <c r="E32" t="n">
-        <v>12.19</v>
+        <v>343.48</v>
       </c>
       <c r="F32" t="n">
-        <v>0.95</v>
+        <v>0.91</v>
+      </c>
+      <c r="G32" t="n">
+        <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Forage maize</t>
+          <t>Forage cabbages</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>5.361562325711099</v>
+        <v>0</v>
       </c>
       <c r="C33" t="b">
         <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>0.84</v>
+        <v>0.68</v>
       </c>
       <c r="E33" t="n">
-        <v>343.48</v>
+        <v>316.8</v>
       </c>
       <c r="F33" t="n">
-        <v>0.91</v>
+        <v>0.04</v>
+      </c>
+      <c r="G33" t="n">
+        <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Forage cabbages</t>
+          <t>Alfalfa and clover</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0</v>
+        <v>0.5577244841048522</v>
       </c>
       <c r="C34" t="b">
         <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>0.68</v>
+        <v>0.57</v>
       </c>
       <c r="E34" t="n">
-        <v>316.8</v>
+        <v>206.43</v>
       </c>
       <c r="F34" t="n">
-        <v>0.04</v>
+        <v>0.67</v>
+      </c>
+      <c r="G34" t="n">
+        <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Alfalfa and clover</t>
+          <t>Non-legume temporary meadow</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.5577244841048522</v>
+        <v>5.36984104852203</v>
       </c>
       <c r="C35" t="b">
         <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="E35" t="n">
-        <v>206.43</v>
+        <v>267.77</v>
       </c>
       <c r="F35" t="n">
-        <v>0.67</v>
+        <v>0.08</v>
+      </c>
+      <c r="G35" t="n">
+        <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Non-legume temporary meadow</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>5.36984104852203</v>
+          <t xml:space="preserve">Natural meadow </t>
+        </is>
       </c>
       <c r="C36" t="b">
         <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>0.62</v>
+        <v>0.89</v>
       </c>
       <c r="E36" t="n">
-        <v>267.77</v>
+        <v>109</v>
       </c>
       <c r="F36" t="n">
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Natural meadow </t>
-        </is>
-      </c>
-      <c r="C37" t="b">
-        <v>0</v>
-      </c>
-      <c r="D37" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="E37" t="n">
-        <v>109</v>
-      </c>
-      <c r="F37" t="n">
         <v>0.52</v>
+      </c>
+      <c r="G36" t="n">
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -1685,9 +1773,6 @@
           <t>Weight for the optimization model</t>
         </is>
       </c>
-      <c r="F2" t="n">
-        <v/>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1703,9 +1788,6 @@
           <t>Weight for the optimization model</t>
         </is>
       </c>
-      <c r="F3" t="n">
-        <v/>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1721,9 +1803,6 @@
           <t>Weight for the optimization model</t>
         </is>
       </c>
-      <c r="F4" t="n">
-        <v/>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1739,9 +1818,6 @@
           <t>Weight for the optimization model</t>
         </is>
       </c>
-      <c r="F5" t="n">
-        <v/>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1757,9 +1833,6 @@
           <t>Weight for the optimization model</t>
         </is>
       </c>
-      <c r="F6" t="n">
-        <v/>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1775,9 +1848,6 @@
           <t>Weight for the optimization model</t>
         </is>
       </c>
-      <c r="F7" t="n">
-        <v/>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1812,9 +1882,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F9" t="n">
-        <v/>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1832,9 +1899,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F10" t="n">
-        <v/>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1852,9 +1916,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F11" t="n">
-        <v/>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1872,9 +1933,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F12" t="n">
-        <v/>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1892,9 +1950,6 @@
           <t>Historical trend</t>
         </is>
       </c>
-      <c r="F13" t="n">
-        <v/>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1912,9 +1967,6 @@
           <t>Historical trend</t>
         </is>
       </c>
-      <c r="F14" t="n">
-        <v/>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1932,9 +1984,6 @@
           <t>Historical trend</t>
         </is>
       </c>
-      <c r="F15" t="n">
-        <v/>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1952,9 +2001,6 @@
           <t>Historical trend</t>
         </is>
       </c>
-      <c r="F16" t="n">
-        <v/>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1972,9 +2018,6 @@
           <t>Historical trend</t>
         </is>
       </c>
-      <c r="F17" t="n">
-        <v/>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1992,9 +2035,6 @@
           <t>Historical trend</t>
         </is>
       </c>
-      <c r="F18" t="n">
-        <v/>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2012,9 +2052,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F19" t="n">
-        <v/>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2032,9 +2069,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F20" t="n">
-        <v/>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2052,9 +2086,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F21" t="n">
-        <v/>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2072,9 +2103,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F22" t="n">
-        <v/>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2092,9 +2120,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F23" t="n">
-        <v/>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2112,9 +2137,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F24" t="n">
-        <v/>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2132,9 +2154,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F25" t="n">
-        <v/>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2152,9 +2171,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F26" t="n">
-        <v/>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2172,9 +2188,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F27" t="n">
-        <v/>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2192,9 +2205,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F28" t="n">
-        <v/>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2212,9 +2222,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F29" t="n">
-        <v/>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2232,9 +2239,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F30" t="n">
-        <v/>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2252,9 +2256,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F31" t="n">
-        <v/>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2272,9 +2273,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F32" t="n">
-        <v/>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2292,9 +2290,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F33" t="n">
-        <v/>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2312,9 +2307,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F34" t="n">
-        <v/>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2332,9 +2324,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F35" t="n">
-        <v/>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2352,9 +2341,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F36" t="n">
-        <v/>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2372,9 +2358,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F37" t="n">
-        <v/>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2392,9 +2375,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F38" t="n">
-        <v/>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2412,9 +2392,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F39" t="n">
-        <v/>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2432,9 +2409,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F40" t="n">
-        <v/>
-      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2452,9 +2426,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F41" t="n">
-        <v/>
-      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2472,9 +2443,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F42" t="n">
-        <v/>
-      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2492,9 +2460,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F43" t="n">
-        <v/>
-      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2512,9 +2477,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F44" t="n">
-        <v/>
-      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2532,9 +2494,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F45" t="n">
-        <v/>
-      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2552,9 +2511,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F46" t="n">
-        <v/>
-      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2572,9 +2528,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F47" t="n">
-        <v/>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2592,9 +2545,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F48" t="n">
-        <v/>
-      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2612,9 +2562,6 @@
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F49" t="n">
-        <v/>
-      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2632,9 +2579,6 @@
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F50" t="n">
-        <v/>
-      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2652,9 +2596,6 @@
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F51" t="n">
-        <v/>
-      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2672,9 +2613,6 @@
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F52" t="n">
-        <v/>
-      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2692,9 +2630,6 @@
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F53" t="n">
-        <v/>
-      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2712,9 +2647,6 @@
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F54" t="n">
-        <v/>
-      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2732,9 +2664,6 @@
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F55" t="n">
-        <v/>
-      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2752,9 +2681,6 @@
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F56" t="n">
-        <v/>
-      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2772,9 +2698,6 @@
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F57" t="n">
-        <v/>
-      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2792,9 +2715,6 @@
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F58" t="n">
-        <v/>
-      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2815,9 +2735,6 @@
           <t>Adapted from ONRB data</t>
         </is>
       </c>
-      <c r="F59" t="n">
-        <v/>
-      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2838,9 +2755,6 @@
           <t>Adapted from ONRB data</t>
         </is>
       </c>
-      <c r="F60" t="n">
-        <v/>
-      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2861,9 +2775,6 @@
           <t>Adapted from ONRB data</t>
         </is>
       </c>
-      <c r="F61" t="n">
-        <v/>
-      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2884,9 +2795,6 @@
           <t>Adapted from ONRB data</t>
         </is>
       </c>
-      <c r="F62" t="n">
-        <v/>
-      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2906,9 +2814,6 @@
         <is>
           <t>Adapted from ONRB data</t>
         </is>
-      </c>
-      <c r="F63" t="n">
-        <v/>
       </c>
     </row>
   </sheetData>
